--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>71.60380000000001</v>
+        <v>75.2821</v>
       </c>
       <c r="E2" t="n">
-        <v>73.0896</v>
+        <v>81.2462</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.486</v>
+        <v>-5.964</v>
       </c>
       <c r="G2" t="n">
-        <v>28.7896</v>
+        <v>24.0468</v>
       </c>
       <c r="H2" t="n">
-        <v>28.564</v>
+        <v>27.3252</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2257999999999998</v>
+        <v>-3.2785</v>
       </c>
       <c r="J2" t="n">
-        <v>53.6789</v>
+        <v>57.0218</v>
       </c>
       <c r="K2" t="n">
-        <v>41.7</v>
+        <v>43.3184</v>
       </c>
       <c r="L2" t="n">
-        <v>11.9788</v>
+        <v>13.703</v>
       </c>
       <c r="M2" t="n">
-        <v>-24.889</v>
+        <v>-32.975</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.1359</v>
+        <v>-15.9937</v>
       </c>
       <c r="O2" t="n">
-        <v>-11.7531</v>
+        <v>-16.9816</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5877</v>
+        <v>5.9183</v>
       </c>
       <c r="Q2" t="n">
-        <v>-35.8396</v>
+        <v>-37.5592</v>
       </c>
       <c r="R2" t="n">
-        <v>37.4275</v>
+        <v>43.4777</v>
       </c>
       <c r="S2" t="n">
-        <v>14.8603</v>
+        <v>18.1307</v>
       </c>
       <c r="T2" t="n">
-        <v>7.4617</v>
+        <v>8.1973</v>
       </c>
       <c r="U2" t="n">
-        <v>7.3989</v>
+        <v>9.9339</v>
       </c>
       <c r="V2" t="n">
-        <v>26.3662</v>
+        <v>27.1862</v>
       </c>
       <c r="W2" t="n">
-        <v>47.789</v>
+        <v>53.5866</v>
       </c>
       <c r="X2" t="n">
-        <v>-21.4232</v>
+        <v>-26.4007</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>28.2474</v>
+        <v>28.9283</v>
       </c>
       <c r="E3" t="n">
-        <v>35.8058</v>
+        <v>36.2995</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.5582</v>
+        <v>-7.371200000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.6428</v>
+        <v>-9.2959</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2464</v>
+        <v>6.030099999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-8.889099999999999</v>
+        <v>-15.3263</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7076</v>
+        <v>26.4903</v>
       </c>
       <c r="K3" t="n">
-        <v>17.4091</v>
+        <v>23.4017</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2982</v>
+        <v>3.0882</v>
       </c>
       <c r="M3" t="n">
-        <v>-23.3499</v>
+        <v>-35.7863</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.1625</v>
+        <v>-17.3715</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.1875</v>
+        <v>-18.4146</v>
       </c>
       <c r="P3" t="n">
-        <v>19.9614</v>
+        <v>26.6331</v>
       </c>
       <c r="Q3" t="n">
-        <v>-12.249</v>
+        <v>-15.2514</v>
       </c>
       <c r="R3" t="n">
-        <v>32.2105</v>
+        <v>41.8845</v>
       </c>
       <c r="S3" t="n">
-        <v>12.8056</v>
+        <v>12.9074</v>
       </c>
       <c r="T3" t="n">
-        <v>9.125500000000001</v>
+        <v>6.0514</v>
       </c>
       <c r="U3" t="n">
-        <v>3.6806</v>
+        <v>6.8564</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8769</v>
+        <v>-1.316299999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>18.2223</v>
+        <v>19.0092</v>
       </c>
       <c r="X3" t="n">
-        <v>-20.0991</v>
+        <v>-20.3254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8377</v>
+        <v>23.7637</v>
       </c>
       <c r="E4" t="n">
-        <v>15.0177</v>
+        <v>27.9357</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8203</v>
+        <v>-4.172</v>
       </c>
       <c r="G4" t="n">
-        <v>13.106</v>
+        <v>-8.878899999999998</v>
       </c>
       <c r="H4" t="n">
-        <v>5.262799999999999</v>
+        <v>-4.9559</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8433</v>
+        <v>-3.9225</v>
       </c>
       <c r="J4" t="n">
-        <v>34.3237</v>
+        <v>22.4516</v>
       </c>
       <c r="K4" t="n">
-        <v>15.1939</v>
+        <v>10.3748</v>
       </c>
       <c r="L4" t="n">
-        <v>19.13</v>
+        <v>12.0769</v>
       </c>
       <c r="M4" t="n">
-        <v>-21.2181</v>
+        <v>-31.3302</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.931000000000001</v>
+        <v>-15.3309</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.2868</v>
+        <v>-15.9991</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.9392</v>
+        <v>25.0396</v>
       </c>
       <c r="Q4" t="n">
-        <v>-40.8303</v>
+        <v>-15.9342</v>
       </c>
       <c r="R4" t="n">
-        <v>32.8908</v>
+        <v>40.9742</v>
       </c>
       <c r="S4" t="n">
-        <v>11.6514</v>
+        <v>4.1381</v>
       </c>
       <c r="T4" t="n">
-        <v>5.6465</v>
+        <v>-2.7226</v>
       </c>
       <c r="U4" t="n">
-        <v>6.0048</v>
+        <v>6.8609</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01929999999999987</v>
+        <v>3.4649</v>
       </c>
       <c r="W4" t="n">
-        <v>15.8767</v>
+        <v>24.1413</v>
       </c>
       <c r="X4" t="n">
-        <v>-15.8575</v>
+        <v>-20.6763</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>W. VAN BECK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>16.6323</v>
+        <v>13.8678</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9751</v>
+        <v>27.5197</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6567999999999996</v>
+        <v>-13.6519</v>
       </c>
       <c r="G5" t="n">
-        <v>20.6277</v>
+        <v>20.2507</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5296</v>
+        <v>-5.342</v>
       </c>
       <c r="I5" t="n">
-        <v>18.0978</v>
+        <v>25.5929</v>
       </c>
       <c r="J5" t="n">
-        <v>39.156</v>
+        <v>41.3402</v>
       </c>
       <c r="K5" t="n">
-        <v>12.2294</v>
+        <v>0.1134999999999997</v>
       </c>
       <c r="L5" t="n">
-        <v>26.9266</v>
+        <v>41.2265</v>
       </c>
       <c r="M5" t="n">
-        <v>-18.5285</v>
+        <v>-21.0893</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.6996</v>
+        <v>-5.4555</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.8293</v>
+        <v>-15.634</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.175800000000001</v>
+        <v>-9.560599999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-39.4691</v>
+        <v>-29.1371</v>
       </c>
       <c r="R5" t="n">
-        <v>36.2934</v>
+        <v>19.5766</v>
       </c>
       <c r="S5" t="n">
-        <v>-14.1701</v>
+        <v>-7.7793</v>
       </c>
       <c r="T5" t="n">
-        <v>-10.5794</v>
+        <v>-5.398099999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.591</v>
+        <v>-2.3812</v>
       </c>
       <c r="V5" t="n">
-        <v>13.3503</v>
+        <v>10.9572</v>
       </c>
       <c r="W5" t="n">
-        <v>26.8672</v>
+        <v>20.715</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.517</v>
+        <v>-9.7578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>9.1814</v>
+        <v>8.8134</v>
       </c>
       <c r="E6" t="n">
-        <v>20.1452</v>
+        <v>12.3038</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.9638</v>
+        <v>-3.4901</v>
       </c>
       <c r="G6" t="n">
-        <v>21.9474</v>
+        <v>16.1819</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0041</v>
+        <v>-3.7802</v>
       </c>
       <c r="I6" t="n">
-        <v>23.9516</v>
+        <v>19.9623</v>
       </c>
       <c r="J6" t="n">
-        <v>36.3684</v>
+        <v>41.3308</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3348</v>
+        <v>8.979800000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>35.0338</v>
+        <v>32.351</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.421</v>
+        <v>-25.1486</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.3388</v>
+        <v>-12.7602</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.0824</v>
+        <v>-12.3887</v>
       </c>
       <c r="P6" t="n">
-        <v>-12.4759</v>
+        <v>-3.8699</v>
       </c>
       <c r="Q6" t="n">
-        <v>-26.5395</v>
+        <v>-45.5266</v>
       </c>
       <c r="R6" t="n">
-        <v>14.0638</v>
+        <v>41.6569</v>
       </c>
       <c r="S6" t="n">
-        <v>-10.0085</v>
+        <v>-16.3795</v>
       </c>
       <c r="T6" t="n">
-        <v>-6.7173</v>
+        <v>-12.574</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.2913</v>
+        <v>-3.805000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>9.7182</v>
+        <v>12.8801</v>
       </c>
       <c r="W6" t="n">
-        <v>17.033</v>
+        <v>29.0733</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.3149</v>
+        <v>-16.1933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>6.106600000000002</v>
+        <v>4.258500000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>19.4171</v>
+        <v>10.1343</v>
       </c>
       <c r="F7" t="n">
-        <v>-13.3105</v>
+        <v>-5.8761</v>
       </c>
       <c r="G7" t="n">
-        <v>41.5538</v>
+        <v>-17.7858</v>
       </c>
       <c r="H7" t="n">
-        <v>19.5659</v>
+        <v>-13.753</v>
       </c>
       <c r="I7" t="n">
-        <v>21.9879</v>
+        <v>-4.0328</v>
       </c>
       <c r="J7" t="n">
-        <v>71.9436</v>
+        <v>10.9466</v>
       </c>
       <c r="K7" t="n">
-        <v>36.0064</v>
+        <v>1.7911</v>
       </c>
       <c r="L7" t="n">
-        <v>35.9369</v>
+        <v>9.1561</v>
       </c>
       <c r="M7" t="n">
-        <v>-30.3896</v>
+        <v>-28.7322</v>
       </c>
       <c r="N7" t="n">
-        <v>-16.4406</v>
+        <v>-15.5443</v>
       </c>
       <c r="O7" t="n">
-        <v>-13.9495</v>
+        <v>-13.1883</v>
       </c>
       <c r="P7" t="n">
-        <v>-40.3762</v>
+        <v>15.9343</v>
       </c>
       <c r="Q7" t="n">
-        <v>-78.9379</v>
+        <v>-19.8043</v>
       </c>
       <c r="R7" t="n">
-        <v>38.5617</v>
+        <v>35.7382</v>
       </c>
       <c r="S7" t="n">
-        <v>-12.7656</v>
+        <v>-2.6685</v>
       </c>
       <c r="T7" t="n">
-        <v>-10.9964</v>
+        <v>-4.045</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.7689</v>
+        <v>1.3769</v>
       </c>
       <c r="V7" t="n">
-        <v>17.6945</v>
+        <v>8.7784</v>
       </c>
       <c r="W7" t="n">
-        <v>37.4078</v>
+        <v>23.0366</v>
       </c>
       <c r="X7" t="n">
-        <v>-19.7134</v>
+        <v>-14.2583</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>5.519600000000001</v>
+        <v>3.545299999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>8.9993</v>
+        <v>14.702</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4795</v>
+        <v>-11.1568</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9974</v>
+        <v>7.974600000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.6463</v>
+        <v>4.1499</v>
       </c>
       <c r="I8" t="n">
-        <v>8.643599999999999</v>
+        <v>3.8249</v>
       </c>
       <c r="J8" t="n">
-        <v>11.4598</v>
+        <v>39.7104</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7024</v>
+        <v>19.9095</v>
       </c>
       <c r="L8" t="n">
-        <v>9.757400000000001</v>
+        <v>19.8012</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.462400000000001</v>
+        <v>-31.7358</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.3487</v>
+        <v>-15.7595</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1138</v>
+        <v>-15.9762</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8147</v>
+        <v>-10.4711</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7.4856</v>
+        <v>-49.1686</v>
       </c>
       <c r="R8" t="n">
-        <v>5.6708</v>
+        <v>38.6976</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.8295</v>
+        <v>14.2663</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.8772</v>
+        <v>6.8977</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04770000000000002</v>
+        <v>7.3688</v>
       </c>
       <c r="V8" t="n">
-        <v>7.166600000000001</v>
+        <v>-8.225000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>8.902100000000001</v>
+        <v>17.2619</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7356</v>
+        <v>-25.4871</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>4.4024</v>
+        <v>0.7368000000000006</v>
       </c>
       <c r="E9" t="n">
-        <v>10.4301</v>
+        <v>6.7194</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.0279</v>
+        <v>-5.9827</v>
       </c>
       <c r="G9" t="n">
-        <v>-16.9545</v>
+        <v>-0.9058000000000006</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.0199</v>
+        <v>-9.624600000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.9349</v>
+        <v>8.7187</v>
       </c>
       <c r="J9" t="n">
-        <v>10.7916</v>
+        <v>19.9598</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1256</v>
+        <v>3.0797</v>
       </c>
       <c r="L9" t="n">
-        <v>8.666</v>
+        <v>16.8803</v>
       </c>
       <c r="M9" t="n">
-        <v>-27.746</v>
+        <v>-20.8658</v>
       </c>
       <c r="N9" t="n">
-        <v>-15.1453</v>
+        <v>-12.704</v>
       </c>
       <c r="O9" t="n">
-        <v>-12.6008</v>
+        <v>-8.161799999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>15.6515</v>
+        <v>-0.6829000000000003</v>
       </c>
       <c r="Q9" t="n">
-        <v>-18.6006</v>
+        <v>-18.4382</v>
       </c>
       <c r="R9" t="n">
-        <v>34.2518</v>
+        <v>17.7554</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.695</v>
+        <v>-10.5904</v>
       </c>
       <c r="T9" t="n">
-        <v>-4.3216</v>
+        <v>-9.9117</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6268</v>
+        <v>-0.6782999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>8.400600000000001</v>
+        <v>12.9159</v>
       </c>
       <c r="W9" t="n">
-        <v>22.5605</v>
+        <v>15.1097</v>
       </c>
       <c r="X9" t="n">
-        <v>-14.1598</v>
+        <v>-2.1938</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>M. SANGARE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.7682</v>
+        <v>0.5199</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4376</v>
+        <v>0.4646</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3302</v>
+        <v>0.0553</v>
       </c>
       <c r="G10" t="n">
-        <v>-13.317</v>
+        <v>0.6778</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.7671</v>
+        <v>0.6778</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.5497</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>6.222099999999999</v>
+        <v>0.5343</v>
       </c>
       <c r="K10" t="n">
-        <v>1.33</v>
+        <v>0.5343</v>
       </c>
       <c r="L10" t="n">
-        <v>4.8924</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-19.539</v>
+        <v>0.1435</v>
       </c>
       <c r="N10" t="n">
-        <v>-9.0969</v>
+        <v>0.1435</v>
       </c>
       <c r="O10" t="n">
-        <v>-10.4418</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>19.2808</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-13.1563</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>32.4373</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8998</v>
+        <v>-0.3856</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.9581</v>
+        <v>-0.0697</v>
       </c>
       <c r="U10" t="n">
-        <v>4.0581</v>
+        <v>-0.3159</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2959999999999998</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>15.3299</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-15.626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SANGARE</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5209</v>
+        <v>0.1579</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4673</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0537</v>
+        <v>0.1579</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6782</v>
+        <v>0.1579</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6782</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5368000000000001</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5368000000000001</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1414</v>
+        <v>0.1579</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1414</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3841</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0696</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3145</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>X. LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1573</v>
+        <v>-0.2421</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1573</v>
+        <v>-0.1724</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1573</v>
+        <v>-0.1724</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0.1724</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1573</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1573</v>
+        <v>-0.1724</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.1724</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1573</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1390,10 +1390,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>K. YEBO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7242</v>
+        <v>-0.4044</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2718</v>
+        <v>1.5551</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.9961</v>
+        <v>-1.9595</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4735</v>
+        <v>-1.3413</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7137</v>
+        <v>-0.2986</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7597</v>
+        <v>-1.0426</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9036</v>
+        <v>-0.6257</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0087</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.895</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4302</v>
+        <v>-0.7155</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2951</v>
+        <v>-0.3881</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1353</v>
+        <v>-0.3275</v>
       </c>
       <c r="P13" t="n">
-        <v>3.8562</v>
+        <v>1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>5.2171</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4299</v>
+        <v>0.9776</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7288000000000002</v>
+        <v>1.0914</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1587</v>
+        <v>-0.1137</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.624000000000001</v>
+        <v>-1.6342</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.624000000000001</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SASTRE</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.499099999999999</v>
+        <v>-0.6837000000000004</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1094999999999997</v>
+        <v>13.2173</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6084</v>
+        <v>-13.9008</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8233000000000001</v>
+        <v>41.4562</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.036799999999999</v>
+        <v>16.694</v>
       </c>
       <c r="I14" t="n">
-        <v>7.2133</v>
+        <v>24.7622</v>
       </c>
       <c r="J14" t="n">
-        <v>9.421900000000001</v>
+        <v>77.6418</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.05080000000000007</v>
+        <v>35.9759</v>
       </c>
       <c r="L14" t="n">
-        <v>9.472199999999999</v>
+        <v>41.6657</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.2454</v>
+        <v>-36.1855</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.985799999999999</v>
+        <v>-19.2819</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2595</v>
+        <v>-16.9036</v>
       </c>
       <c r="P14" t="n">
-        <v>16.7855</v>
+        <v>-50.7618</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.8049</v>
+        <v>-94.01179999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>23.5907</v>
+        <v>43.2503</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.0245</v>
+        <v>-12.8544</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.014699999999999</v>
+        <v>-11.5121</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.0099</v>
+        <v>-1.3423</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.4368</v>
+        <v>21.4763</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5068</v>
+        <v>41.0991</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.9437</v>
+        <v>-19.6229</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.1317</v>
+        <v>-3.1169</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0643</v>
+        <v>1.049</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.196</v>
+        <v>-4.1661</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9779</v>
+        <v>0.9821</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8845999999999999</v>
+        <v>0.8819</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09330000000000005</v>
+        <v>0.1002000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2651</v>
+        <v>1.2526</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1531</v>
+        <v>1.1409</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2871</v>
+        <v>-0.2705</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2685</v>
+        <v>-0.2590000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.01870000000000005</v>
+        <v>-0.01149999999999995</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537000000000001</v>
+        <v>-0.4553000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1684</v>
+        <v>0.1695</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3871</v>
+        <v>0.3899</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2187</v>
+        <v>-0.2205</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.8244</v>
+        <v>-3.8132</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.370699999999999</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. BORDON</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.275</v>
+        <v>-3.8969</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.777</v>
+        <v>9.184600000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.502</v>
+        <v>-13.0815</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8697</v>
+        <v>-1.619</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.713</v>
+        <v>-7.104</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1567</v>
+        <v>5.484800000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.6225</v>
+        <v>31.5331</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.5452</v>
+        <v>14.0189</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.07730000000000004</v>
+        <v>17.5142</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2472</v>
+        <v>-33.1522</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8322000000000001</v>
+        <v>-21.1229</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0795</v>
+        <v>-12.0294</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4535999999999999</v>
+        <v>28.454</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2684</v>
+        <v>-19.3485</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7219</v>
+        <v>47.8028</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.3128</v>
+        <v>-8.6234</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8862</v>
+        <v>-11.7309</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4266</v>
+        <v>3.1076</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-22.1087</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>8.731</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-30.8392</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>E. FRIDRIKSSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.0015</v>
+        <v>-4.1529</v>
       </c>
       <c r="E17" t="n">
-        <v>8.198399999999999</v>
+        <v>-1.363</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.2001</v>
+        <v>-2.7899</v>
       </c>
       <c r="G17" t="n">
-        <v>1.302299999999999</v>
+        <v>-5.7648</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.2425</v>
+        <v>1.468</v>
       </c>
       <c r="I17" t="n">
-        <v>8.544600000000001</v>
+        <v>-7.2327</v>
       </c>
       <c r="J17" t="n">
-        <v>29.9045</v>
+        <v>-0.9758</v>
       </c>
       <c r="K17" t="n">
-        <v>11.4386</v>
+        <v>3.6952</v>
       </c>
       <c r="L17" t="n">
-        <v>18.4665</v>
+        <v>-4.671</v>
       </c>
       <c r="M17" t="n">
-        <v>-28.6021</v>
+        <v>-4.7889</v>
       </c>
       <c r="N17" t="n">
-        <v>-18.6808</v>
+        <v>-2.2272</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.9215</v>
+        <v>-2.5617</v>
       </c>
       <c r="P17" t="n">
-        <v>22.6832</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-19.0538</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>41.7371</v>
+        <v>2.7316</v>
       </c>
       <c r="S17" t="n">
-        <v>-8.2689</v>
+        <v>-0.8434</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.626300000000001</v>
+        <v>-0.6556</v>
       </c>
       <c r="U17" t="n">
-        <v>1.358</v>
+        <v>-0.1878</v>
       </c>
       <c r="V17" t="n">
-        <v>-21.7186</v>
+        <v>1.0894</v>
       </c>
       <c r="W17" t="n">
-        <v>6.974</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
-        <v>-28.6926</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,148 +1810,382 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.1421</v>
+        <v>-5.219199999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.115400000000001</v>
+        <v>4.9766</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.0266</v>
+        <v>-10.1959</v>
       </c>
       <c r="G18" t="n">
-        <v>8.9476</v>
+        <v>1.2886</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9316999999999998</v>
+        <v>1.6929</v>
       </c>
       <c r="I18" t="n">
-        <v>9.879299999999999</v>
+        <v>-0.4046000000000003</v>
       </c>
       <c r="J18" t="n">
-        <v>28.9771</v>
+        <v>7.812399999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>11.1351</v>
+        <v>3.4647</v>
       </c>
       <c r="L18" t="n">
-        <v>17.8421</v>
+        <v>4.348</v>
       </c>
       <c r="M18" t="n">
-        <v>-20.0294</v>
+        <v>-6.5242</v>
       </c>
       <c r="N18" t="n">
-        <v>-12.0668</v>
+        <v>-1.7716</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.9629</v>
+        <v>-4.7524</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.495099999999999</v>
+        <v>7.511900000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>-43.3251</v>
+        <v>-2.9592</v>
       </c>
       <c r="R18" t="n">
-        <v>40.8298</v>
+        <v>10.471</v>
       </c>
       <c r="S18" t="n">
-        <v>-23.6302</v>
+        <v>0.0719999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-15.2641</v>
+        <v>0.1234000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-8.366300000000001</v>
+        <v>-0.05130000000000012</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9645000000000006</v>
+        <v>-14.0916</v>
       </c>
       <c r="W18" t="n">
-        <v>22.4962</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-23.4607</v>
+        <v>-14.0916</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>D. BORDON</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>La Laguna Tenerife</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-6.9237</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-6.590100000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.3336000000000001</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-4.1466</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1.4131</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-2.7336</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-3.217</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1.5555</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.6614</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.9296</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1425000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.0722</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2.2764</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.7315</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-2.6875</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.0967</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.5908</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.5447</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.5447</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>J. SASTRE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>La Laguna Tenerife</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-10.7308</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-1.762399999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-8.968499999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-7.492299999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-9.914899999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.4223</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8.847899999999999</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.5092999999999999</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9.3575</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-16.3405</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-9.4057</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-6.9348</v>
+      </c>
+      <c r="P20" t="n">
+        <v>18.6658</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-7.0565</v>
+      </c>
+      <c r="R20" t="n">
+        <v>25.7227</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-10.9258</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-6.0484</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-4.8775</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-10.9787</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.4946</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-13.4732</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>B. FITIPALDO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>La Laguna Tenerife</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-19.5377</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.9021999999999997</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-18.636</v>
+      </c>
+      <c r="G21" t="n">
+        <v>17.2739</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.648</v>
+      </c>
+      <c r="I21" t="n">
+        <v>15.626</v>
+      </c>
+      <c r="J21" t="n">
+        <v>44.8001</v>
+      </c>
+      <c r="K21" t="n">
+        <v>16.5813</v>
+      </c>
+      <c r="L21" t="n">
+        <v>28.2185</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-27.5258</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-14.9331</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-12.5931</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-3.6418</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-51.8999</v>
+      </c>
+      <c r="R21" t="n">
+        <v>48.258</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-28.0228</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-18.8745</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-9.148099999999999</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-5.1466</v>
+      </c>
+      <c r="W21" t="n">
+        <v>25.0726</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-30.2193</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>La Laguna Tenerife</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>28</v>
-      </c>
-      <c r="D19" t="n">
-        <v>129.204</v>
-      </c>
-      <c r="E19" t="n">
-        <v>202.5364</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-73.33279999999999</v>
-      </c>
-      <c r="G19" t="n">
-        <v>107.9514</v>
-      </c>
-      <c r="H19" t="n">
-        <v>20.0838</v>
-      </c>
-      <c r="I19" t="n">
-        <v>87.86709999999999</v>
-      </c>
-      <c r="J19" t="n">
-        <v>357.0382</v>
-      </c>
-      <c r="K19" t="n">
-        <v>153.7079</v>
-      </c>
-      <c r="L19" t="n">
-        <v>203.3306</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-249.0862</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-133.6227</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-115.4651</v>
-      </c>
-      <c r="P19" t="n">
-        <v>31.7561</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-347.0553</v>
-      </c>
-      <c r="R19" t="n">
-        <v>378.8115</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-50.93320000000001</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-49.96129999999999</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.9710000000000019</v>
-      </c>
-      <c r="V19" t="n">
-        <v>40.4282</v>
-      </c>
-      <c r="W19" t="n">
-        <v>242.5118</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-202.0845</v>
+      <c r="C22" t="n">
+        <v>34</v>
+      </c>
+      <c r="D22" t="n">
+        <v>104.9654</v>
+      </c>
+      <c r="E22" t="n">
+        <v>236.6204</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-131.6558</v>
+      </c>
+      <c r="G22" t="n">
+        <v>72.88770000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.209099999999996</v>
+      </c>
+      <c r="I22" t="n">
+        <v>68.67859999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>426.8552</v>
+      </c>
+      <c r="K22" t="n">
+        <v>184.4043</v>
+      </c>
+      <c r="L22" t="n">
+        <v>242.4512</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-353.9669</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-180.1955</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-173.7726</v>
+      </c>
+      <c r="P22" t="n">
+        <v>52.3556</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-410.8759</v>
+      </c>
+      <c r="R22" t="n">
+        <v>463.2328999999999</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-51.1687</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-61.9579</v>
+      </c>
+      <c r="U22" t="n">
+        <v>10.79209999999999</v>
+      </c>
+      <c r="V22" t="n">
+        <v>30.8894</v>
+      </c>
+      <c r="W22" t="n">
+        <v>282.5993</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-251.7099</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_La Laguna Tenerife.xlsx
@@ -565,13 +565,13 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>75.2821</v>
+        <v>59.4788</v>
       </c>
       <c r="E2" t="n">
-        <v>81.2462</v>
+        <v>70.92789999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.964</v>
+        <v>-11.4489</v>
       </c>
       <c r="G2" t="n">
         <v>24.0468</v>
@@ -610,13 +610,13 @@
         <v>43.4777</v>
       </c>
       <c r="S2" t="n">
-        <v>18.1307</v>
+        <v>2.327399999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>8.1973</v>
+        <v>-2.1215</v>
       </c>
       <c r="U2" t="n">
-        <v>9.9339</v>
+        <v>4.4491</v>
       </c>
       <c r="V2" t="n">
         <v>27.1862</v>
@@ -643,13 +643,13 @@
         <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>28.9283</v>
+        <v>21.982</v>
       </c>
       <c r="E3" t="n">
-        <v>36.2995</v>
+        <v>30.8865</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.371200000000001</v>
+        <v>-8.903799999999999</v>
       </c>
       <c r="G3" t="n">
         <v>-9.2959</v>
@@ -688,13 +688,13 @@
         <v>41.8845</v>
       </c>
       <c r="S3" t="n">
-        <v>12.9074</v>
+        <v>5.9617</v>
       </c>
       <c r="T3" t="n">
-        <v>6.0514</v>
+        <v>0.6379999999999998</v>
       </c>
       <c r="U3" t="n">
-        <v>6.8564</v>
+        <v>5.3236</v>
       </c>
       <c r="V3" t="n">
         <v>-1.316299999999999</v>
@@ -721,13 +721,13 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>23.7637</v>
+        <v>21.3159</v>
       </c>
       <c r="E4" t="n">
-        <v>27.9357</v>
+        <v>27.9287</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.172</v>
+        <v>-6.6133</v>
       </c>
       <c r="G4" t="n">
         <v>-8.878899999999998</v>
@@ -766,13 +766,13 @@
         <v>40.9742</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1381</v>
+        <v>1.6901</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.7226</v>
+        <v>-2.7298</v>
       </c>
       <c r="U4" t="n">
-        <v>6.8609</v>
+        <v>4.4197</v>
       </c>
       <c r="V4" t="n">
         <v>3.4649</v>
@@ -799,13 +799,13 @@
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>13.8678</v>
+        <v>19.4116</v>
       </c>
       <c r="E5" t="n">
-        <v>27.5197</v>
+        <v>30.0491</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.6519</v>
+        <v>-10.6374</v>
       </c>
       <c r="G5" t="n">
         <v>20.2507</v>
@@ -844,13 +844,13 @@
         <v>19.5766</v>
       </c>
       <c r="S5" t="n">
-        <v>-7.7793</v>
+        <v>-2.2359</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.398099999999999</v>
+        <v>-2.869</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.3812</v>
+        <v>0.6330999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>10.9572</v>
@@ -877,13 +877,13 @@
         <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>8.8134</v>
+        <v>18.3595</v>
       </c>
       <c r="E6" t="n">
-        <v>12.3038</v>
+        <v>19.8989</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.4901</v>
+        <v>-1.539300000000001</v>
       </c>
       <c r="G6" t="n">
         <v>16.1819</v>
@@ -922,13 +922,13 @@
         <v>41.6569</v>
       </c>
       <c r="S6" t="n">
-        <v>-16.3795</v>
+        <v>-6.833299999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-12.574</v>
+        <v>-4.9797</v>
       </c>
       <c r="U6" t="n">
-        <v>-3.805000000000001</v>
+        <v>-1.8537</v>
       </c>
       <c r="V6" t="n">
         <v>12.8801</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>4.258500000000001</v>
+        <v>8.4335</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1343</v>
+        <v>11.527</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.8761</v>
+        <v>-3.0938</v>
       </c>
       <c r="G7" t="n">
-        <v>-17.7858</v>
+        <v>-0.9058000000000006</v>
       </c>
       <c r="H7" t="n">
-        <v>-13.753</v>
+        <v>-9.624600000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.0328</v>
+        <v>8.7187</v>
       </c>
       <c r="J7" t="n">
-        <v>10.9466</v>
+        <v>19.9598</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7911</v>
+        <v>3.0797</v>
       </c>
       <c r="L7" t="n">
-        <v>9.1561</v>
+        <v>16.8803</v>
       </c>
       <c r="M7" t="n">
-        <v>-28.7322</v>
+        <v>-20.8658</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.5443</v>
+        <v>-12.704</v>
       </c>
       <c r="O7" t="n">
-        <v>-13.1883</v>
+        <v>-8.161799999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>15.9343</v>
+        <v>-0.6829000000000003</v>
       </c>
       <c r="Q7" t="n">
-        <v>-19.8043</v>
+        <v>-18.4382</v>
       </c>
       <c r="R7" t="n">
-        <v>35.7382</v>
+        <v>17.7554</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.6685</v>
+        <v>-2.8938</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.045</v>
+        <v>-5.1045</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3769</v>
+        <v>2.2104</v>
       </c>
       <c r="V7" t="n">
-        <v>8.7784</v>
+        <v>12.9159</v>
       </c>
       <c r="W7" t="n">
-        <v>23.0366</v>
+        <v>15.1097</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.2583</v>
+        <v>-2.1938</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>3.545299999999999</v>
+        <v>5.706799999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>14.702</v>
+        <v>16.6873</v>
       </c>
       <c r="F8" t="n">
-        <v>-11.1568</v>
+        <v>-10.9807</v>
       </c>
       <c r="G8" t="n">
-        <v>7.974600000000001</v>
+        <v>41.4562</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1499</v>
+        <v>16.694</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8249</v>
+        <v>24.7622</v>
       </c>
       <c r="J8" t="n">
-        <v>39.7104</v>
+        <v>77.6418</v>
       </c>
       <c r="K8" t="n">
-        <v>19.9095</v>
+        <v>35.9759</v>
       </c>
       <c r="L8" t="n">
-        <v>19.8012</v>
+        <v>41.6657</v>
       </c>
       <c r="M8" t="n">
-        <v>-31.7358</v>
+        <v>-36.1855</v>
       </c>
       <c r="N8" t="n">
-        <v>-15.7595</v>
+        <v>-19.2819</v>
       </c>
       <c r="O8" t="n">
-        <v>-15.9762</v>
+        <v>-16.9036</v>
       </c>
       <c r="P8" t="n">
-        <v>-10.4711</v>
+        <v>-50.7618</v>
       </c>
       <c r="Q8" t="n">
-        <v>-49.1686</v>
+        <v>-94.01179999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>38.6976</v>
+        <v>43.2503</v>
       </c>
       <c r="S8" t="n">
-        <v>14.2663</v>
+        <v>-6.4642</v>
       </c>
       <c r="T8" t="n">
-        <v>6.8977</v>
+        <v>-8.042199999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>7.3688</v>
+        <v>1.5782</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.225000000000001</v>
+        <v>21.4763</v>
       </c>
       <c r="W8" t="n">
-        <v>17.2619</v>
+        <v>41.0991</v>
       </c>
       <c r="X8" t="n">
-        <v>-25.4871</v>
+        <v>-19.6229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7368000000000006</v>
+        <v>1.9717</v>
       </c>
       <c r="E9" t="n">
-        <v>6.7194</v>
+        <v>8.1556</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.9827</v>
+        <v>-6.184</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9058000000000006</v>
+        <v>-17.7858</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.624600000000001</v>
+        <v>-13.753</v>
       </c>
       <c r="I9" t="n">
-        <v>8.7187</v>
+        <v>-4.0328</v>
       </c>
       <c r="J9" t="n">
-        <v>19.9598</v>
+        <v>10.9466</v>
       </c>
       <c r="K9" t="n">
-        <v>3.0797</v>
+        <v>1.7911</v>
       </c>
       <c r="L9" t="n">
-        <v>16.8803</v>
+        <v>9.1561</v>
       </c>
       <c r="M9" t="n">
-        <v>-20.8658</v>
+        <v>-28.7322</v>
       </c>
       <c r="N9" t="n">
-        <v>-12.704</v>
+        <v>-15.5443</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.161799999999999</v>
+        <v>-13.1883</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6829000000000003</v>
+        <v>15.9343</v>
       </c>
       <c r="Q9" t="n">
-        <v>-18.4382</v>
+        <v>-19.8043</v>
       </c>
       <c r="R9" t="n">
-        <v>17.7554</v>
+        <v>35.7382</v>
       </c>
       <c r="S9" t="n">
-        <v>-10.5904</v>
+        <v>-4.955</v>
       </c>
       <c r="T9" t="n">
-        <v>-9.9117</v>
+        <v>-6.023400000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6782999999999999</v>
+        <v>1.0686</v>
       </c>
       <c r="V9" t="n">
-        <v>12.9159</v>
+        <v>8.7784</v>
       </c>
       <c r="W9" t="n">
-        <v>15.1097</v>
+        <v>23.0366</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1938</v>
+        <v>-14.2583</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5199</v>
+        <v>0.5896</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4646</v>
+        <v>0.5343</v>
       </c>
       <c r="F10" t="n">
         <v>0.0553</v>
@@ -1234,10 +1234,10 @@
         <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3856</v>
+        <v>-0.3159</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0697</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>-0.3159</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. YEBO</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4044</v>
+        <v>-0.7512999999999996</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5551</v>
+        <v>11.9162</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9595</v>
+        <v>-12.6671</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3413</v>
+        <v>-1.619</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2986</v>
+        <v>-7.104</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0426</v>
+        <v>5.484800000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6257</v>
+        <v>31.5331</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08939999999999999</v>
+        <v>14.0189</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7151999999999999</v>
+        <v>17.5142</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7155</v>
+        <v>-33.1522</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3881</v>
+        <v>-21.1229</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3275</v>
+        <v>-12.0294</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5934</v>
+        <v>28.454</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-19.3485</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5934</v>
+        <v>47.8028</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9776</v>
+        <v>-5.4775</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0914</v>
+        <v>-8.9994</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1137</v>
+        <v>3.522</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.6342</v>
+        <v>-22.1087</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0895</v>
+        <v>8.731</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7237</v>
+        <v>-30.8392</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>K. YEBO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6837000000000004</v>
+        <v>-1.021</v>
       </c>
       <c r="E14" t="n">
-        <v>13.2173</v>
+        <v>0.8444</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.9008</v>
+        <v>-1.8654</v>
       </c>
       <c r="G14" t="n">
-        <v>41.4562</v>
+        <v>-1.3413</v>
       </c>
       <c r="H14" t="n">
-        <v>16.694</v>
+        <v>-0.2986</v>
       </c>
       <c r="I14" t="n">
-        <v>24.7622</v>
+        <v>-1.0426</v>
       </c>
       <c r="J14" t="n">
-        <v>77.6418</v>
+        <v>-0.6257</v>
       </c>
       <c r="K14" t="n">
-        <v>35.9759</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>41.6657</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-36.1855</v>
+        <v>-0.7155</v>
       </c>
       <c r="N14" t="n">
-        <v>-19.2819</v>
+        <v>-0.3881</v>
       </c>
       <c r="O14" t="n">
-        <v>-16.9036</v>
+        <v>-0.3275</v>
       </c>
       <c r="P14" t="n">
-        <v>-50.7618</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
-        <v>-94.01179999999999</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>43.2503</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-12.8544</v>
+        <v>0.3611</v>
       </c>
       <c r="T14" t="n">
-        <v>-11.5121</v>
+        <v>0.3807</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3423</v>
+        <v>-0.0196</v>
       </c>
       <c r="V14" t="n">
-        <v>21.4763</v>
+        <v>-1.6342</v>
       </c>
       <c r="W14" t="n">
-        <v>41.0991</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-19.6229</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.1169</v>
+        <v>-1.596099999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.049</v>
+        <v>8.9366</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.1661</v>
+        <v>-10.5322</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9821</v>
+        <v>17.2739</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8819</v>
+        <v>1.648</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1002000000000001</v>
+        <v>15.626</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2526</v>
+        <v>44.8001</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1409</v>
+        <v>16.5813</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1117</v>
+        <v>28.2185</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2705</v>
+        <v>-27.5258</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2590000000000001</v>
+        <v>-14.9331</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.01149999999999995</v>
+        <v>-12.5931</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4553000000000001</v>
+        <v>-3.6418</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1382</v>
+        <v>-51.8999</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6829</v>
+        <v>48.258</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1695</v>
+        <v>-10.0813</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3899</v>
+        <v>-9.0365</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2205</v>
+        <v>-1.0448</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.8132</v>
+        <v>-5.1466</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5447</v>
+        <v>25.0726</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.3579</v>
+        <v>-30.2193</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.8969</v>
+        <v>-3.0228</v>
       </c>
       <c r="E16" t="n">
-        <v>9.184600000000001</v>
+        <v>1.0491</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.0815</v>
+        <v>-4.0719</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.619</v>
+        <v>0.9821</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.104</v>
+        <v>0.8819</v>
       </c>
       <c r="I16" t="n">
-        <v>5.484800000000001</v>
+        <v>0.1002000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>31.5331</v>
+        <v>1.2526</v>
       </c>
       <c r="K16" t="n">
-        <v>14.0189</v>
+        <v>1.1409</v>
       </c>
       <c r="L16" t="n">
-        <v>17.5142</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-33.1522</v>
+        <v>-0.2705</v>
       </c>
       <c r="N16" t="n">
-        <v>-21.1229</v>
+        <v>-0.2590000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.0294</v>
+        <v>-0.01149999999999995</v>
       </c>
       <c r="P16" t="n">
-        <v>28.454</v>
+        <v>-0.4553000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-19.3485</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>47.8028</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-8.6234</v>
+        <v>0.2635</v>
       </c>
       <c r="T16" t="n">
-        <v>-11.7309</v>
+        <v>0.39</v>
       </c>
       <c r="U16" t="n">
-        <v>3.1076</v>
+        <v>-0.1263</v>
       </c>
       <c r="V16" t="n">
-        <v>-22.1087</v>
+        <v>-3.8132</v>
       </c>
       <c r="W16" t="n">
-        <v>8.731</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-30.8392</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.1529</v>
+        <v>-3.3969</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.363</v>
+        <v>-0.7010000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.7899</v>
+        <v>-2.6958</v>
       </c>
       <c r="G17" t="n">
         <v>-5.7648</v>
@@ -1780,13 +1780,13 @@
         <v>2.7316</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8434</v>
+        <v>-0.08739999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6556</v>
+        <v>0.0063</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1878</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>1.0894</v>
@@ -1813,13 +1813,13 @@
         <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.219199999999999</v>
+        <v>-4.070799999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>4.9766</v>
+        <v>5.777900000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.1959</v>
+        <v>-9.8484</v>
       </c>
       <c r="G18" t="n">
         <v>1.2886</v>
@@ -1858,13 +1858,13 @@
         <v>10.471</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0719999999999999</v>
+        <v>1.2205</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1234000000000001</v>
+        <v>0.9245999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.05130000000000012</v>
+        <v>0.2961000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>-14.0916</v>
@@ -1891,13 +1891,13 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.9237</v>
+        <v>-6.3765</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.590100000000001</v>
+        <v>-6.2625</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3336000000000001</v>
+        <v>-0.1140000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-4.1466</v>
@@ -1936,13 +1936,13 @@
         <v>2.7315</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.6875</v>
+        <v>-2.1405</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0967</v>
+        <v>-0.7692</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.5908</v>
+        <v>-1.3713</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5447</v>
@@ -1969,13 +1969,13 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-10.7308</v>
+        <v>-6.6589</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.762399999999999</v>
+        <v>0.3624999999999994</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.968499999999999</v>
+        <v>-7.0215</v>
       </c>
       <c r="G20" t="n">
         <v>-7.492299999999999</v>
@@ -2014,13 +2014,13 @@
         <v>25.7227</v>
       </c>
       <c r="S20" t="n">
-        <v>-10.9258</v>
+        <v>-6.8537</v>
       </c>
       <c r="T20" t="n">
-        <v>-6.0484</v>
+        <v>-3.9233</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.8775</v>
+        <v>-2.9304</v>
       </c>
       <c r="V20" t="n">
         <v>-10.9787</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>33</v>
       </c>
       <c r="D21" t="n">
-        <v>-19.5377</v>
+        <v>-8.860400000000002</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9021999999999997</v>
+        <v>5.142899999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.636</v>
+        <v>-14.0038</v>
       </c>
       <c r="G21" t="n">
-        <v>17.2739</v>
+        <v>7.974600000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.648</v>
+        <v>4.1499</v>
       </c>
       <c r="I21" t="n">
-        <v>15.626</v>
+        <v>3.8249</v>
       </c>
       <c r="J21" t="n">
-        <v>44.8001</v>
+        <v>39.7104</v>
       </c>
       <c r="K21" t="n">
-        <v>16.5813</v>
+        <v>19.9095</v>
       </c>
       <c r="L21" t="n">
-        <v>28.2185</v>
+        <v>19.8012</v>
       </c>
       <c r="M21" t="n">
-        <v>-27.5258</v>
+        <v>-31.7358</v>
       </c>
       <c r="N21" t="n">
-        <v>-14.9331</v>
+        <v>-15.7595</v>
       </c>
       <c r="O21" t="n">
-        <v>-12.5931</v>
+        <v>-15.9762</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.6418</v>
+        <v>-10.4711</v>
       </c>
       <c r="Q21" t="n">
-        <v>-51.8999</v>
+        <v>-49.1686</v>
       </c>
       <c r="R21" t="n">
-        <v>48.258</v>
+        <v>38.6976</v>
       </c>
       <c r="S21" t="n">
-        <v>-28.0228</v>
+        <v>1.8607</v>
       </c>
       <c r="T21" t="n">
-        <v>-18.8745</v>
+        <v>-2.6613</v>
       </c>
       <c r="U21" t="n">
-        <v>-9.148099999999999</v>
+        <v>4.5223</v>
       </c>
       <c r="V21" t="n">
-        <v>-5.1466</v>
+        <v>-8.225000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>25.0726</v>
+        <v>17.2619</v>
       </c>
       <c r="X21" t="n">
-        <v>-30.2193</v>
+        <v>-25.4871</v>
       </c>
     </row>
     <row r="22">
@@ -2125,22 +2125,22 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>104.9654</v>
+        <v>121.4105</v>
       </c>
       <c r="E22" t="n">
-        <v>236.6204</v>
+        <v>243.5917</v>
       </c>
       <c r="F22" t="n">
-        <v>-131.6558</v>
+        <v>-122.1805</v>
       </c>
       <c r="G22" t="n">
-        <v>72.88770000000001</v>
+        <v>72.8877</v>
       </c>
       <c r="H22" t="n">
-        <v>4.209099999999996</v>
+        <v>4.209099999999995</v>
       </c>
       <c r="I22" t="n">
-        <v>68.67859999999999</v>
+        <v>68.6786</v>
       </c>
       <c r="J22" t="n">
         <v>426.8552</v>
@@ -2161,22 +2161,22 @@
         <v>-173.7726</v>
       </c>
       <c r="P22" t="n">
-        <v>52.3556</v>
+        <v>52.35559999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-410.8759</v>
       </c>
       <c r="R22" t="n">
-        <v>463.2328999999999</v>
+        <v>463.2329</v>
       </c>
       <c r="S22" t="n">
-        <v>-51.1687</v>
+        <v>-34.72319999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-61.9579</v>
+        <v>-54.98989999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>10.79209999999999</v>
+        <v>20.2674</v>
       </c>
       <c r="V22" t="n">
         <v>30.8894</v>
